--- a/output/pdf_financials_xlsx/UX.xlsx
+++ b/output/pdf_financials_xlsx/UX.xlsx
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.009925</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.009925</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.004963</v>
       </c>
     </row>
     <row r="29">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.786724</v>
+        <v>-0.776799</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.563854</v>
+        <v>-0.553929</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.220302</v>
+        <v>-0.215339</v>
       </c>
     </row>
     <row r="30">
@@ -4210,7 +4210,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5291,7 +5295,11 @@
           <t>Depreciation of right of use asset (note 4)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.009925</v>
       </c>
